--- a/ig/nr-changes/StructureDefinition-as-device.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:25:16+00:00</t>
+    <t>2023-05-03T15:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-changes/StructureDefinition-as-device.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:57:05+00:00</t>
+    <t>2023-05-03T16:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-changes/StructureDefinition-as-device.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T16:01:19+00:00</t>
+    <t>2023-05-03T16:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
